--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/TEXAS_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/TEXAS_2011.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C174">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C249">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C283">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C900">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1049">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1050">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1056">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1191">
@@ -22135,7 +22135,7 @@
         <v>167</v>
       </c>
       <c r="D1210">
-        <v>0.000972298233561</v>
+        <v>0.0009722982335610002</v>
       </c>
     </row>
     <row r="1211">
@@ -24889,7 +24889,7 @@
         <v>1601</v>
       </c>
       <c r="D1363">
-        <v>0.009321254322943</v>
+        <v>0.009321254322943002</v>
       </c>
     </row>
     <row r="1364">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1504">
@@ -28158,7 +28158,7 @@
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1545">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1718">
